--- a/data/excel/acciones_energia_mensual.xlsx
+++ b/data/excel/acciones_energia_mensual.xlsx
@@ -490,17 +490,17 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur (TGS) (TGS), cierre de fin de mes en dólares</t>
+          <t>Transportadora de Gas del Sur (TGS), cierre de fin de mes en dólares</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur (TGS) (TGS), var. % mensual</t>
+          <t>Transportadora de Gas del Sur (TGS), var. % mensual</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Transportadora de Gas del Sur (TGS) (TGS), var. % interanual</t>
+          <t>Transportadora de Gas del Sur (TGS), var. % interanual</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29T12:36:56Z</t>
+          <t>2026-10-30T06:28:30Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/acciones_energia_mensual.xlsx
+++ b/data/excel/acciones_energia_mensual.xlsx
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30T06:28:30Z</t>
+          <t>2026-10-31T06:18:29Z</t>
         </is>
       </c>
     </row>
